--- a/TURFv6/revC/TURFv6_revC_BOM_041525.xlsx
+++ b/TURFv6/revC/TURFv6_revC_BOM_041525.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\pueo-daq-design\TURFv6\revC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\pueo-daq-design\TURFv6\revC\archive\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{460175AE-6B72-4B5B-93F1-8D2BD67D19CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B91AEC9-C212-48BB-BC63-D40E691D44E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D3B74482-F8A5-4E82-A69B-8579953A21D8}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="294">
   <si>
     <t>Item</t>
   </si>
@@ -104,6 +104,9 @@
     <t>Zetex</t>
   </si>
   <si>
+    <t>N-Channel 30 V 0.08 Ohm Surface Mount Enhancement Mode MOSFET - SOT-23</t>
+  </si>
+  <si>
     <t>J23</t>
   </si>
   <si>
@@ -188,9 +191,6 @@
     <t>CAPACITOR_LST,0.1u</t>
   </si>
   <si>
-    <t>generic</t>
-  </si>
-  <si>
     <t>0402 0.1u cap</t>
   </si>
   <si>
@@ -518,9 +518,6 @@
     <t>R1 R25</t>
   </si>
   <si>
-    <t>RESISTOR,31</t>
-  </si>
-  <si>
     <t>R192</t>
   </si>
   <si>
@@ -539,9 +536,6 @@
     <t>RESISTOR,5.36k</t>
   </si>
   <si>
-    <t>R30-32 R52 R54 R59 R61 R63 R65</t>
-  </si>
-  <si>
     <t>RESISTOR,DNP</t>
   </si>
   <si>
@@ -626,9 +620,6 @@
     <t>18V, 5A, 42mO eFuse With Integrated Reverse Current Protection and DevSleep Support 20-WQFN -40 to 85</t>
   </si>
   <si>
-    <t>U7 U18</t>
-  </si>
-  <si>
     <t>TXU0202DCUR</t>
   </si>
   <si>
@@ -749,9 +740,6 @@
     <t>0402 100 ohm resistor</t>
   </si>
   <si>
-    <t>R3-9 R11-13 R16-19 R23 R34-36 R40-42 R48-50 R55-58 R60 R62 R64 R66 R69 R75-76</t>
-  </si>
-  <si>
     <t>0402 15k resistor</t>
   </si>
   <si>
@@ -764,9 +752,6 @@
     <t>0402 2k resistor</t>
   </si>
   <si>
-    <t>0402 31 ohm resistor</t>
-  </si>
-  <si>
     <t>R14-15 R22</t>
   </si>
   <si>
@@ -797,12 +782,6 @@
     <t>0402 35.7k resistor</t>
   </si>
   <si>
-    <t>RESISTOR,459k</t>
-  </si>
-  <si>
-    <t>0402 459k resistor</t>
-  </si>
-  <si>
     <t>0402 5.36k resistor</t>
   </si>
   <si>
@@ -812,38 +791,140 @@
     <t>Lumex</t>
   </si>
   <si>
+    <t>RESISTOR,30.9</t>
+  </si>
+  <si>
+    <t>RESISTOR,453k</t>
+  </si>
+  <si>
+    <t>0402 30.9 ohm resistor</t>
+  </si>
+  <si>
+    <t>0402 453k resistor</t>
+  </si>
+  <si>
+    <t>R3-9 R11-13 R16-19 R23 R34-36 R40-42 R48-50 R55-56 R58 R60 R62 R64 R66 R69 R75-76</t>
+  </si>
+  <si>
+    <t>U7</t>
+  </si>
+  <si>
+    <t>U18</t>
+  </si>
+  <si>
+    <t>0201X104K160CT</t>
+  </si>
+  <si>
+    <t>Walsin</t>
+  </si>
+  <si>
+    <t>0402B104K160CT</t>
+  </si>
+  <si>
+    <t>0603X106M100CT</t>
+  </si>
+  <si>
+    <t>KGM05ACG1H120JN</t>
+  </si>
+  <si>
+    <t>Kyocera</t>
+  </si>
+  <si>
+    <t>0402X105K250CT</t>
+  </si>
+  <si>
+    <t>GRM155R71H472KA01D</t>
+  </si>
+  <si>
+    <t>CL05A475MP5NRNC</t>
+  </si>
+  <si>
+    <t>Samsung</t>
+  </si>
+  <si>
+    <t>C3216X5R1E476M160AC</t>
+  </si>
+  <si>
+    <t>TDK</t>
+  </si>
+  <si>
+    <t>WR04X000 PTL</t>
+  </si>
+  <si>
+    <t>RC0402FR-071K02L</t>
+  </si>
+  <si>
+    <t>Yageo</t>
+  </si>
+  <si>
+    <t>RC0402FR-07100RL</t>
+  </si>
+  <si>
+    <t>WR04X1002FTL</t>
+  </si>
+  <si>
+    <t>WR04X1202FTL</t>
+  </si>
+  <si>
+    <t>WR04X1502FTL</t>
+  </si>
+  <si>
+    <t>CR0402-FX-1622GLF</t>
+  </si>
+  <si>
+    <t>Bourns</t>
+  </si>
+  <si>
+    <t>RC0402FR-0726K7L</t>
+  </si>
+  <si>
+    <t>WR04X2001FTL</t>
+  </si>
+  <si>
+    <t>RC0402FR-0730R9L</t>
+  </si>
+  <si>
+    <t>AC0402FR-0731K6L</t>
+  </si>
+  <si>
+    <t>RC0402FR-1335K7L</t>
+  </si>
+  <si>
+    <t>R30-32 R52 R54 R57 R59 R61 R63 R65</t>
+  </si>
+  <si>
+    <t>RC0402FR-07453KL</t>
+  </si>
+  <si>
+    <t>RC0402FR-075K1L</t>
+  </si>
+  <si>
+    <t>RC0402FR-075K36L</t>
+  </si>
+  <si>
+    <t>Q1-2</t>
+  </si>
+  <si>
+    <t>Q3-7</t>
+  </si>
+  <si>
+    <t>N-Channel 30 V 2.9A (Ta) 1W (Ta) Surface Mount SOT-23-3</t>
+  </si>
+  <si>
     <t>QSH-120-01-L-D-A</t>
   </si>
   <si>
+    <t>LMZ22008TZ/NOPB</t>
+  </si>
+  <si>
     <t>100 Position Connector Header, Outer Shroud Contacts Surface Mount Gold</t>
-  </si>
-  <si>
-    <t>LMZ22008TZ/NOPB</t>
-  </si>
-  <si>
-    <t>Q1-2</t>
-  </si>
-  <si>
-    <t>Onsemi</t>
-  </si>
-  <si>
-    <t>MOSFET N-CH 60V 115MA SOT23-3</t>
-  </si>
-  <si>
-    <t>Q3-7</t>
-  </si>
-  <si>
-    <t>N-Channel 30 V 2.9A (Ta) 1W (Ta) Surface Mount SOT-23-3</t>
-  </si>
-  <si>
-    <t>156.25 MHz oscillator</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -851,25 +932,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -881,16 +950,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Neutral" xfId="1" builtinId="28"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -904,10 +970,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1227,7 +1289,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3CEAF1D-FC24-46C3-81E9-8108BDA594C0}">
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.5546875" bestFit="1" customWidth="1"/>
@@ -1262,26 +1324,26 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1339,41 +1401,41 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>261</v>
+        <v>288</v>
       </c>
       <c r="D5" t="s">
         <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>262</v>
+        <v>21</v>
       </c>
       <c r="G5" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="1">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="1" t="s">
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1385,19 +1447,19 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -1408,19 +1470,19 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -1431,64 +1493,64 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F9" t="s">
         <v>17</v>
       </c>
       <c r="G9" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="1" t="s">
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
+      <c r="D10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="1">
-        <v>1</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="1" t="s">
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="1" t="s">
+      <c r="D11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1500,19 +1562,19 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -1523,41 +1585,38 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F13" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="1">
-        <v>1</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="1" t="s">
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G14" s="1" t="s">
+      <c r="D14" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1569,19 +1628,19 @@
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E15" t="s">
-        <v>50</v>
+        <v>258</v>
       </c>
       <c r="F15" t="s">
-        <v>50</v>
+        <v>259</v>
       </c>
       <c r="G15" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -1592,16 +1651,16 @@
         <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E16" t="s">
-        <v>50</v>
+        <v>260</v>
       </c>
       <c r="F16" t="s">
-        <v>50</v>
+        <v>259</v>
       </c>
       <c r="G16" t="s">
         <v>51</v>
@@ -1615,19 +1674,19 @@
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D17" t="s">
         <v>53</v>
       </c>
       <c r="E17" t="s">
-        <v>50</v>
+        <v>261</v>
       </c>
       <c r="F17" t="s">
-        <v>50</v>
+        <v>259</v>
       </c>
       <c r="G17" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -1644,13 +1703,13 @@
         <v>55</v>
       </c>
       <c r="E18" t="s">
-        <v>50</v>
+        <v>262</v>
       </c>
       <c r="F18" t="s">
-        <v>50</v>
+        <v>263</v>
       </c>
       <c r="G18" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -1661,16 +1720,16 @@
         <v>6</v>
       </c>
       <c r="C19" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D19" t="s">
         <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>50</v>
+        <v>264</v>
       </c>
       <c r="F19" t="s">
-        <v>50</v>
+        <v>259</v>
       </c>
       <c r="G19" t="s">
         <v>57</v>
@@ -1684,19 +1743,19 @@
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D20" t="s">
         <v>58</v>
       </c>
       <c r="E20" t="s">
-        <v>50</v>
+        <v>265</v>
       </c>
       <c r="F20" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G20" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -1707,19 +1766,19 @@
         <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D21" t="s">
         <v>59</v>
       </c>
       <c r="E21" t="s">
-        <v>50</v>
+        <v>266</v>
       </c>
       <c r="F21" t="s">
-        <v>50</v>
+        <v>267</v>
       </c>
       <c r="G21" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -1736,13 +1795,13 @@
         <v>61</v>
       </c>
       <c r="E22" t="s">
-        <v>50</v>
+        <v>268</v>
       </c>
       <c r="F22" t="s">
-        <v>50</v>
+        <v>269</v>
       </c>
       <c r="G22" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -1768,49 +1827,49 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="1">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24">
         <v>6</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" t="s">
         <v>67</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" t="s">
         <v>68</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="1">
+      <c r="E24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" t="s">
+        <v>9</v>
+      </c>
+      <c r="G24" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="1">
-        <v>1</v>
-      </c>
-      <c r="C25" s="1" t="s">
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
         <v>69</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" t="s">
         <v>70</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G25" s="1" t="s">
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" t="s">
+        <v>9</v>
+      </c>
+      <c r="G25" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1903,7 +1962,7 @@
         <v>82</v>
       </c>
       <c r="G29" t="s">
-        <v>259</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -1929,49 +1988,49 @@
         <v>90</v>
       </c>
     </row>
-    <row r="31" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="1">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="1">
-        <v>1</v>
-      </c>
-      <c r="C31" s="1" t="s">
+      <c r="B31">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
         <v>91</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" t="s">
         <v>92</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="1">
+      <c r="E31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" t="s">
+        <v>9</v>
+      </c>
+      <c r="G31" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32">
         <v>2</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" t="s">
         <v>93</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" t="s">
         <v>94</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G32" s="1" t="s">
+      <c r="E32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" t="s">
+        <v>9</v>
+      </c>
+      <c r="G32" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2015,7 +2074,7 @@
         <v>101</v>
       </c>
       <c r="F34" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G34" t="s">
         <v>102</v>
@@ -2035,7 +2094,7 @@
         <v>104</v>
       </c>
       <c r="E35" t="s">
-        <v>260</v>
+        <v>292</v>
       </c>
       <c r="F35" t="s">
         <v>105</v>
@@ -2090,49 +2149,49 @@
         <v>113</v>
       </c>
     </row>
-    <row r="38" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="1">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B38">
         <v>2</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" t="s">
         <v>114</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" t="s">
         <v>115</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="1">
+      <c r="E38" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" t="s">
+        <v>9</v>
+      </c>
+      <c r="G38" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B39">
         <v>2</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" t="s">
         <v>116</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" t="s">
         <v>117</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G39" s="1" t="s">
+      <c r="E39" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" t="s">
+        <v>9</v>
+      </c>
+      <c r="G39" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2159,26 +2218,26 @@
         <v>121</v>
       </c>
     </row>
-    <row r="41" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="1">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B41">
         <v>28</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" t="s">
         <v>122</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" t="s">
         <v>123</v>
       </c>
-      <c r="E41" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G41" s="1" t="s">
+      <c r="E41" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" t="s">
+        <v>9</v>
+      </c>
+      <c r="G41" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2288,7 +2347,7 @@
         <v>142</v>
       </c>
       <c r="E46" t="s">
-        <v>258</v>
+        <v>291</v>
       </c>
       <c r="F46" t="s">
         <v>82</v>
@@ -2311,13 +2370,13 @@
         <v>145</v>
       </c>
       <c r="E47" t="s">
-        <v>50</v>
+        <v>270</v>
       </c>
       <c r="F47" t="s">
-        <v>50</v>
+        <v>259</v>
       </c>
       <c r="G47" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
@@ -2334,13 +2393,13 @@
         <v>147</v>
       </c>
       <c r="E48" t="s">
-        <v>50</v>
+        <v>271</v>
       </c>
       <c r="F48" t="s">
-        <v>50</v>
+        <v>272</v>
       </c>
       <c r="G48" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
@@ -2357,13 +2416,13 @@
         <v>149</v>
       </c>
       <c r="E49" t="s">
-        <v>50</v>
+        <v>273</v>
       </c>
       <c r="F49" t="s">
-        <v>50</v>
+        <v>272</v>
       </c>
       <c r="G49" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
@@ -2371,19 +2430,19 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C50" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="D50" t="s">
         <v>150</v>
       </c>
       <c r="E50" t="s">
-        <v>50</v>
+        <v>274</v>
       </c>
       <c r="F50" t="s">
-        <v>50</v>
+        <v>259</v>
       </c>
       <c r="G50" t="s">
         <v>151</v>
@@ -2403,13 +2462,13 @@
         <v>153</v>
       </c>
       <c r="E51" t="s">
-        <v>50</v>
+        <v>275</v>
       </c>
       <c r="F51" t="s">
-        <v>50</v>
+        <v>259</v>
       </c>
       <c r="G51" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
@@ -2426,13 +2485,13 @@
         <v>155</v>
       </c>
       <c r="E52" t="s">
-        <v>50</v>
+        <v>276</v>
       </c>
       <c r="F52" t="s">
-        <v>50</v>
+        <v>259</v>
       </c>
       <c r="G52" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
@@ -2443,19 +2502,19 @@
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D53" t="s">
         <v>156</v>
       </c>
       <c r="E53" t="s">
-        <v>50</v>
+        <v>277</v>
       </c>
       <c r="F53" t="s">
-        <v>50</v>
+        <v>278</v>
       </c>
       <c r="G53" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
@@ -2466,19 +2525,19 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D54" t="s">
         <v>157</v>
       </c>
       <c r="E54" t="s">
-        <v>50</v>
+        <v>279</v>
       </c>
       <c r="F54" t="s">
-        <v>50</v>
+        <v>272</v>
       </c>
       <c r="G54" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
@@ -2489,19 +2548,19 @@
         <v>9</v>
       </c>
       <c r="C55" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D55" t="s">
         <v>158</v>
       </c>
       <c r="E55" t="s">
-        <v>50</v>
+        <v>280</v>
       </c>
       <c r="F55" t="s">
-        <v>50</v>
+        <v>259</v>
       </c>
       <c r="G55" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
@@ -2515,16 +2574,16 @@
         <v>159</v>
       </c>
       <c r="D56" t="s">
-        <v>160</v>
+        <v>251</v>
       </c>
       <c r="E56" t="s">
-        <v>50</v>
+        <v>281</v>
       </c>
       <c r="F56" t="s">
-        <v>50</v>
+        <v>272</v>
       </c>
       <c r="G56" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
@@ -2535,19 +2594,19 @@
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D57" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="E57" t="s">
-        <v>50</v>
+        <v>282</v>
       </c>
       <c r="F57" t="s">
-        <v>50</v>
+        <v>272</v>
       </c>
       <c r="G57" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
@@ -2558,19 +2617,19 @@
         <v>1</v>
       </c>
       <c r="C58" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D58" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="E58" t="s">
-        <v>50</v>
+        <v>283</v>
       </c>
       <c r="F58" t="s">
-        <v>50</v>
+        <v>272</v>
       </c>
       <c r="G58" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
@@ -2581,16 +2640,16 @@
         <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D59" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E59" t="s">
-        <v>50</v>
+        <v>285</v>
       </c>
       <c r="F59" t="s">
-        <v>50</v>
+        <v>272</v>
       </c>
       <c r="G59" t="s">
         <v>254</v>
@@ -2604,19 +2663,19 @@
         <v>3</v>
       </c>
       <c r="C60" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="D60" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E60" t="s">
-        <v>50</v>
+        <v>286</v>
       </c>
       <c r="F60" t="s">
-        <v>50</v>
+        <v>272</v>
       </c>
       <c r="G60" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
@@ -2627,41 +2686,41 @@
         <v>1</v>
       </c>
       <c r="C61" t="s">
+        <v>164</v>
+      </c>
+      <c r="D61" t="s">
         <v>165</v>
       </c>
-      <c r="D61" t="s">
+      <c r="E61" t="s">
+        <v>287</v>
+      </c>
+      <c r="F61" t="s">
+        <v>272</v>
+      </c>
+      <c r="G61" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <v>9</v>
+      </c>
+      <c r="C62" t="s">
+        <v>284</v>
+      </c>
+      <c r="D62" t="s">
         <v>166</v>
       </c>
-      <c r="E61" t="s">
-        <v>50</v>
-      </c>
-      <c r="F61" t="s">
-        <v>50</v>
-      </c>
-      <c r="G61" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="1">
-        <v>61</v>
-      </c>
-      <c r="B62" s="1">
-        <v>9</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G62" s="1" t="s">
+      <c r="E62" t="s">
+        <v>9</v>
+      </c>
+      <c r="F62" t="s">
+        <v>9</v>
+      </c>
+      <c r="G62" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2673,41 +2732,41 @@
         <v>1</v>
       </c>
       <c r="C63" t="s">
+        <v>167</v>
+      </c>
+      <c r="D63" t="s">
+        <v>168</v>
+      </c>
+      <c r="E63" t="s">
         <v>169</v>
       </c>
-      <c r="D63" t="s">
+      <c r="F63" t="s">
         <v>170</v>
       </c>
-      <c r="E63" t="s">
+      <c r="G63" t="s">
         <v>171</v>
       </c>
-      <c r="F63" t="s">
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <v>1</v>
+      </c>
+      <c r="C64" t="s">
         <v>172</v>
       </c>
-      <c r="G63" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="1">
-        <v>63</v>
-      </c>
-      <c r="B64" s="1">
-        <v>1</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G64" s="1" t="s">
+      <c r="D64" t="s">
+        <v>168</v>
+      </c>
+      <c r="E64" t="s">
+        <v>9</v>
+      </c>
+      <c r="F64" t="s">
+        <v>9</v>
+      </c>
+      <c r="G64" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2719,19 +2778,19 @@
         <v>1</v>
       </c>
       <c r="C65" t="s">
+        <v>173</v>
+      </c>
+      <c r="D65" t="s">
+        <v>174</v>
+      </c>
+      <c r="E65" t="s">
+        <v>249</v>
+      </c>
+      <c r="F65" t="s">
+        <v>250</v>
+      </c>
+      <c r="G65" t="s">
         <v>175</v>
-      </c>
-      <c r="D65" t="s">
-        <v>176</v>
-      </c>
-      <c r="E65" t="s">
-        <v>256</v>
-      </c>
-      <c r="F65" t="s">
-        <v>257</v>
-      </c>
-      <c r="G65" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
@@ -2742,19 +2801,19 @@
         <v>4</v>
       </c>
       <c r="C66" t="s">
+        <v>176</v>
+      </c>
+      <c r="D66" t="s">
+        <v>174</v>
+      </c>
+      <c r="E66" t="s">
+        <v>177</v>
+      </c>
+      <c r="F66" t="s">
         <v>178</v>
       </c>
-      <c r="D66" t="s">
-        <v>176</v>
-      </c>
-      <c r="E66" t="s">
+      <c r="G66" t="s">
         <v>179</v>
-      </c>
-      <c r="F66" t="s">
-        <v>180</v>
-      </c>
-      <c r="G66" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
@@ -2765,19 +2824,19 @@
         <v>1</v>
       </c>
       <c r="C67" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D67" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E67" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F67" t="s">
         <v>105</v>
       </c>
       <c r="G67" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
@@ -2788,19 +2847,19 @@
         <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D68" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E68" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F68" t="s">
         <v>105</v>
       </c>
       <c r="G68" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
@@ -2811,19 +2870,19 @@
         <v>3</v>
       </c>
       <c r="C69" t="s">
+        <v>186</v>
+      </c>
+      <c r="D69" t="s">
+        <v>187</v>
+      </c>
+      <c r="E69" t="s">
+        <v>187</v>
+      </c>
+      <c r="F69" t="s">
         <v>188</v>
       </c>
-      <c r="D69" t="s">
+      <c r="G69" t="s">
         <v>189</v>
-      </c>
-      <c r="E69" t="s">
-        <v>189</v>
-      </c>
-      <c r="F69" t="s">
-        <v>190</v>
-      </c>
-      <c r="G69" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
@@ -2834,19 +2893,19 @@
         <v>1</v>
       </c>
       <c r="C70" t="s">
+        <v>190</v>
+      </c>
+      <c r="D70" t="s">
+        <v>191</v>
+      </c>
+      <c r="E70" t="s">
         <v>192</v>
-      </c>
-      <c r="D70" t="s">
-        <v>193</v>
-      </c>
-      <c r="E70" t="s">
-        <v>194</v>
       </c>
       <c r="F70" t="s">
         <v>105</v>
       </c>
       <c r="G70" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
@@ -2854,22 +2913,22 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C71" t="s">
-        <v>196</v>
+        <v>256</v>
       </c>
       <c r="D71" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E71" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F71" t="s">
         <v>105</v>
       </c>
       <c r="G71" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
@@ -2880,19 +2939,19 @@
         <v>1</v>
       </c>
       <c r="C72" t="s">
-        <v>199</v>
+        <v>257</v>
       </c>
       <c r="D72" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="E72" t="s">
-        <v>200</v>
+        <v>9</v>
       </c>
       <c r="F72" t="s">
-        <v>105</v>
+        <v>9</v>
       </c>
       <c r="G72" t="s">
-        <v>201</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
@@ -2903,19 +2962,19 @@
         <v>1</v>
       </c>
       <c r="C73" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D73" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="E73" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="F73" t="s">
-        <v>17</v>
+        <v>105</v>
       </c>
       <c r="G73" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
@@ -2926,19 +2985,19 @@
         <v>1</v>
       </c>
       <c r="C74" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D74" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E74" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="F74" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="G74" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
@@ -2949,19 +3008,19 @@
         <v>1</v>
       </c>
       <c r="C75" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D75" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E75" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="F75" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="G75" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
@@ -2972,19 +3031,19 @@
         <v>1</v>
       </c>
       <c r="C76" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="D76" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="E76" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="F76" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="G76" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
@@ -2995,19 +3054,19 @@
         <v>1</v>
       </c>
       <c r="C77" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D77" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="E77" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="F77" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="G77" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
@@ -3015,26 +3074,48 @@
         <v>77</v>
       </c>
       <c r="B78">
+        <v>1</v>
+      </c>
+      <c r="C78" t="s">
+        <v>214</v>
+      </c>
+      <c r="D78" t="s">
+        <v>215</v>
+      </c>
+      <c r="E78" t="s">
+        <v>216</v>
+      </c>
+      <c r="F78" t="s">
+        <v>212</v>
+      </c>
+      <c r="G78" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79">
         <v>4</v>
       </c>
-      <c r="C78" t="s">
-        <v>264</v>
-      </c>
-      <c r="D78" t="s">
+      <c r="C79" t="s">
+        <v>289</v>
+      </c>
+      <c r="D79" t="s">
         <v>19</v>
       </c>
-      <c r="E78" t="s">
+      <c r="E79" t="s">
         <v>20</v>
       </c>
-      <c r="F78" t="s">
+      <c r="F79" t="s">
         <v>21</v>
       </c>
-      <c r="G78" t="s">
-        <v>265</v>
+      <c r="G79" t="s">
+        <v>290</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/TURFv6/revC/TURFv6_revC_BOM_041525.xlsx
+++ b/TURFv6/revC/TURFv6_revC_BOM_041525.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\pueo-daq-design\TURFv6\revC\archive\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\pueo-daq-design\TURFv6\revC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B91AEC9-C212-48BB-BC63-D40E691D44E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EECFFCB-E100-435C-AE6A-156FCECF6241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D3B74482-F8A5-4E82-A69B-8579953A21D8}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="295">
   <si>
     <t>Item</t>
   </si>
@@ -104,9 +104,6 @@
     <t>Zetex</t>
   </si>
   <si>
-    <t>N-Channel 30 V 0.08 Ohm Surface Mount Enhancement Mode MOSFET - SOT-23</t>
-  </si>
-  <si>
     <t>J23</t>
   </si>
   <si>
@@ -918,6 +915,12 @@
   </si>
   <si>
     <t>100 Position Connector Header, Outer Shroud Contacts Surface Mount Gold</t>
+  </si>
+  <si>
+    <t>Onsemi</t>
+  </si>
+  <si>
+    <t>MOSFET N-CH 60V 115MA SOT23-3</t>
   </si>
 </sst>
 </file>
@@ -1401,19 +1404,19 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D5" t="s">
         <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>21</v>
+        <v>293</v>
       </c>
       <c r="G5" t="s">
-        <v>22</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1424,10 +1427,10 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
         <v>23</v>
-      </c>
-      <c r="D6" t="s">
-        <v>24</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1447,19 +1450,19 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
         <v>25</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>26</v>
-      </c>
-      <c r="E7" t="s">
-        <v>27</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -1470,19 +1473,19 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" t="s">
         <v>29</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" t="s">
         <v>30</v>
       </c>
-      <c r="E8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>31</v>
-      </c>
-      <c r="G8" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -1493,19 +1496,19 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
         <v>33</v>
       </c>
-      <c r="D9" t="s">
-        <v>34</v>
-      </c>
       <c r="E9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F9" t="s">
         <v>17</v>
       </c>
       <c r="G9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -1516,10 +1519,10 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s">
         <v>36</v>
-      </c>
-      <c r="D10" t="s">
-        <v>37</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1539,10 +1542,10 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" t="s">
         <v>38</v>
-      </c>
-      <c r="D11" t="s">
-        <v>39</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1562,19 +1565,19 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
         <v>40</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" t="s">
         <v>41</v>
       </c>
-      <c r="E12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>42</v>
-      </c>
-      <c r="G12" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -1585,16 +1588,16 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" t="s">
         <v>44</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>45</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>46</v>
-      </c>
-      <c r="F13" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -1605,10 +1608,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" t="s">
         <v>48</v>
-      </c>
-      <c r="D14" t="s">
-        <v>49</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -1628,19 +1631,19 @@
         <v>18</v>
       </c>
       <c r="C15" t="s">
+        <v>218</v>
+      </c>
+      <c r="D15" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" t="s">
+        <v>257</v>
+      </c>
+      <c r="F15" t="s">
+        <v>258</v>
+      </c>
+      <c r="G15" t="s">
         <v>219</v>
-      </c>
-      <c r="D15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E15" t="s">
-        <v>258</v>
-      </c>
-      <c r="F15" t="s">
-        <v>259</v>
-      </c>
-      <c r="G15" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -1651,19 +1654,19 @@
         <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D16" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" t="s">
+        <v>259</v>
+      </c>
+      <c r="F16" t="s">
+        <v>258</v>
+      </c>
+      <c r="G16" t="s">
         <v>50</v>
-      </c>
-      <c r="E16" t="s">
-        <v>260</v>
-      </c>
-      <c r="F16" t="s">
-        <v>259</v>
-      </c>
-      <c r="G16" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -1674,19 +1677,19 @@
         <v>3</v>
       </c>
       <c r="C17" t="s">
+        <v>222</v>
+      </c>
+      <c r="D17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" t="s">
+        <v>260</v>
+      </c>
+      <c r="F17" t="s">
+        <v>258</v>
+      </c>
+      <c r="G17" t="s">
         <v>223</v>
-      </c>
-      <c r="D17" t="s">
-        <v>53</v>
-      </c>
-      <c r="E17" t="s">
-        <v>261</v>
-      </c>
-      <c r="F17" t="s">
-        <v>259</v>
-      </c>
-      <c r="G17" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -1697,19 +1700,19 @@
         <v>4</v>
       </c>
       <c r="C18" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" t="s">
         <v>54</v>
       </c>
-      <c r="D18" t="s">
-        <v>55</v>
-      </c>
       <c r="E18" t="s">
+        <v>261</v>
+      </c>
+      <c r="F18" t="s">
         <v>262</v>
       </c>
-      <c r="F18" t="s">
-        <v>263</v>
-      </c>
       <c r="G18" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -1720,19 +1723,19 @@
         <v>6</v>
       </c>
       <c r="C19" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D19" t="s">
+        <v>55</v>
+      </c>
+      <c r="E19" t="s">
+        <v>263</v>
+      </c>
+      <c r="F19" t="s">
+        <v>258</v>
+      </c>
+      <c r="G19" t="s">
         <v>56</v>
-      </c>
-      <c r="E19" t="s">
-        <v>264</v>
-      </c>
-      <c r="F19" t="s">
-        <v>259</v>
-      </c>
-      <c r="G19" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -1743,19 +1746,19 @@
         <v>2</v>
       </c>
       <c r="C20" t="s">
+        <v>225</v>
+      </c>
+      <c r="D20" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" t="s">
+        <v>264</v>
+      </c>
+      <c r="F20" t="s">
+        <v>51</v>
+      </c>
+      <c r="G20" t="s">
         <v>226</v>
-      </c>
-      <c r="D20" t="s">
-        <v>58</v>
-      </c>
-      <c r="E20" t="s">
-        <v>265</v>
-      </c>
-      <c r="F20" t="s">
-        <v>52</v>
-      </c>
-      <c r="G20" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -1766,19 +1769,19 @@
         <v>5</v>
       </c>
       <c r="C21" t="s">
+        <v>227</v>
+      </c>
+      <c r="D21" t="s">
+        <v>58</v>
+      </c>
+      <c r="E21" t="s">
+        <v>265</v>
+      </c>
+      <c r="F21" t="s">
+        <v>266</v>
+      </c>
+      <c r="G21" t="s">
         <v>228</v>
-      </c>
-      <c r="D21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E21" t="s">
-        <v>266</v>
-      </c>
-      <c r="F21" t="s">
-        <v>267</v>
-      </c>
-      <c r="G21" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -1789,19 +1792,19 @@
         <v>2</v>
       </c>
       <c r="C22" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" t="s">
         <v>60</v>
       </c>
-      <c r="D22" t="s">
-        <v>61</v>
-      </c>
       <c r="E22" t="s">
+        <v>267</v>
+      </c>
+      <c r="F22" t="s">
         <v>268</v>
       </c>
-      <c r="F22" t="s">
-        <v>269</v>
-      </c>
       <c r="G22" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -1812,19 +1815,19 @@
         <v>2</v>
       </c>
       <c r="C23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" t="s">
         <v>62</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>63</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>64</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>65</v>
-      </c>
-      <c r="G23" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -1835,10 +1838,10 @@
         <v>6</v>
       </c>
       <c r="C24" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" t="s">
         <v>67</v>
-      </c>
-      <c r="D24" t="s">
-        <v>68</v>
       </c>
       <c r="E24" t="s">
         <v>9</v>
@@ -1858,10 +1861,10 @@
         <v>1</v>
       </c>
       <c r="C25" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" t="s">
         <v>69</v>
-      </c>
-      <c r="D25" t="s">
-        <v>70</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
@@ -1881,19 +1884,19 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26" t="s">
         <v>71</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
+        <v>71</v>
+      </c>
+      <c r="F26" t="s">
         <v>72</v>
       </c>
-      <c r="E26" t="s">
-        <v>72</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
         <v>73</v>
-      </c>
-      <c r="G26" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -1904,19 +1907,19 @@
         <v>5</v>
       </c>
       <c r="C27" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" t="s">
         <v>75</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>76</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>77</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>78</v>
-      </c>
-      <c r="G27" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -1927,19 +1930,19 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
+        <v>79</v>
+      </c>
+      <c r="D28" t="s">
         <v>80</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
+        <v>80</v>
+      </c>
+      <c r="F28" t="s">
         <v>81</v>
       </c>
-      <c r="E28" t="s">
-        <v>81</v>
-      </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>82</v>
-      </c>
-      <c r="G28" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -1950,19 +1953,19 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
+        <v>83</v>
+      </c>
+      <c r="D29" t="s">
         <v>84</v>
       </c>
-      <c r="D29" t="s">
-        <v>85</v>
-      </c>
       <c r="E29" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F29" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G29" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -1973,19 +1976,19 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
+        <v>85</v>
+      </c>
+      <c r="D30" t="s">
         <v>86</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>87</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>88</v>
       </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
         <v>89</v>
-      </c>
-      <c r="G30" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -1996,10 +1999,10 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31" t="s">
         <v>91</v>
-      </c>
-      <c r="D31" t="s">
-        <v>92</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
@@ -2019,10 +2022,10 @@
         <v>2</v>
       </c>
       <c r="C32" t="s">
+        <v>92</v>
+      </c>
+      <c r="D32" t="s">
         <v>93</v>
-      </c>
-      <c r="D32" t="s">
-        <v>94</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
@@ -2042,19 +2045,19 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
+        <v>94</v>
+      </c>
+      <c r="D33" t="s">
         <v>95</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>96</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>97</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>98</v>
-      </c>
-      <c r="G33" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -2065,19 +2068,19 @@
         <v>1</v>
       </c>
       <c r="C34" t="s">
+        <v>99</v>
+      </c>
+      <c r="D34" t="s">
         <v>100</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
+        <v>100</v>
+      </c>
+      <c r="F34" t="s">
+        <v>41</v>
+      </c>
+      <c r="G34" t="s">
         <v>101</v>
-      </c>
-      <c r="E34" t="s">
-        <v>101</v>
-      </c>
-      <c r="F34" t="s">
-        <v>42</v>
-      </c>
-      <c r="G34" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -2088,19 +2091,19 @@
         <v>1</v>
       </c>
       <c r="C35" t="s">
+        <v>102</v>
+      </c>
+      <c r="D35" t="s">
         <v>103</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
+        <v>291</v>
+      </c>
+      <c r="F35" t="s">
         <v>104</v>
       </c>
-      <c r="E35" t="s">
-        <v>292</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="G35" t="s">
         <v>105</v>
-      </c>
-      <c r="G35" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -2111,19 +2114,19 @@
         <v>1</v>
       </c>
       <c r="C36" t="s">
+        <v>106</v>
+      </c>
+      <c r="D36" t="s">
         <v>107</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>108</v>
-      </c>
-      <c r="E36" t="s">
-        <v>109</v>
       </c>
       <c r="F36" t="s">
         <v>17</v>
       </c>
       <c r="G36" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -2134,19 +2137,19 @@
         <v>1</v>
       </c>
       <c r="C37" t="s">
+        <v>110</v>
+      </c>
+      <c r="D37" t="s">
         <v>111</v>
       </c>
-      <c r="D37" t="s">
-        <v>112</v>
-      </c>
       <c r="E37" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F37" t="s">
         <v>17</v>
       </c>
       <c r="G37" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -2157,10 +2160,10 @@
         <v>2</v>
       </c>
       <c r="C38" t="s">
+        <v>113</v>
+      </c>
+      <c r="D38" t="s">
         <v>114</v>
-      </c>
-      <c r="D38" t="s">
-        <v>115</v>
       </c>
       <c r="E38" t="s">
         <v>9</v>
@@ -2180,10 +2183,10 @@
         <v>2</v>
       </c>
       <c r="C39" t="s">
+        <v>115</v>
+      </c>
+      <c r="D39" t="s">
         <v>116</v>
-      </c>
-      <c r="D39" t="s">
-        <v>117</v>
       </c>
       <c r="E39" t="s">
         <v>9</v>
@@ -2203,19 +2206,19 @@
         <v>1</v>
       </c>
       <c r="C40" t="s">
+        <v>117</v>
+      </c>
+      <c r="D40" t="s">
         <v>118</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
+        <v>118</v>
+      </c>
+      <c r="F40" t="s">
         <v>119</v>
       </c>
-      <c r="E40" t="s">
-        <v>119</v>
-      </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>120</v>
-      </c>
-      <c r="G40" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
@@ -2226,10 +2229,10 @@
         <v>28</v>
       </c>
       <c r="C41" t="s">
+        <v>121</v>
+      </c>
+      <c r="D41" t="s">
         <v>122</v>
-      </c>
-      <c r="D41" t="s">
-        <v>123</v>
       </c>
       <c r="E41" t="s">
         <v>9</v>
@@ -2249,19 +2252,19 @@
         <v>1</v>
       </c>
       <c r="C42" t="s">
+        <v>123</v>
+      </c>
+      <c r="D42" t="s">
         <v>124</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
+        <v>124</v>
+      </c>
+      <c r="F42" t="s">
         <v>125</v>
       </c>
-      <c r="E42" t="s">
-        <v>125</v>
-      </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>126</v>
-      </c>
-      <c r="G42" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -2272,19 +2275,19 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
+        <v>127</v>
+      </c>
+      <c r="D43" t="s">
         <v>128</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
         <v>129</v>
       </c>
-      <c r="E43" t="s">
+      <c r="F43" t="s">
+        <v>51</v>
+      </c>
+      <c r="G43" t="s">
         <v>130</v>
-      </c>
-      <c r="F43" t="s">
-        <v>52</v>
-      </c>
-      <c r="G43" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -2295,19 +2298,19 @@
         <v>1</v>
       </c>
       <c r="C44" t="s">
+        <v>131</v>
+      </c>
+      <c r="D44" t="s">
         <v>132</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>133</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" t="s">
         <v>134</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>135</v>
-      </c>
-      <c r="G44" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -2318,19 +2321,19 @@
         <v>1</v>
       </c>
       <c r="C45" t="s">
+        <v>136</v>
+      </c>
+      <c r="D45" t="s">
         <v>137</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>138</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
+        <v>134</v>
+      </c>
+      <c r="G45" t="s">
         <v>139</v>
-      </c>
-      <c r="F45" t="s">
-        <v>135</v>
-      </c>
-      <c r="G45" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -2341,19 +2344,19 @@
         <v>2</v>
       </c>
       <c r="C46" t="s">
+        <v>140</v>
+      </c>
+      <c r="D46" t="s">
         <v>141</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
+        <v>290</v>
+      </c>
+      <c r="F46" t="s">
+        <v>81</v>
+      </c>
+      <c r="G46" t="s">
         <v>142</v>
-      </c>
-      <c r="E46" t="s">
-        <v>291</v>
-      </c>
-      <c r="F46" t="s">
-        <v>82</v>
-      </c>
-      <c r="G46" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -2364,19 +2367,19 @@
         <v>5</v>
       </c>
       <c r="C47" t="s">
+        <v>143</v>
+      </c>
+      <c r="D47" t="s">
         <v>144</v>
       </c>
-      <c r="D47" t="s">
-        <v>145</v>
-      </c>
       <c r="E47" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F47" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G47" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
@@ -2387,19 +2390,19 @@
         <v>1</v>
       </c>
       <c r="C48" t="s">
+        <v>145</v>
+      </c>
+      <c r="D48" t="s">
         <v>146</v>
       </c>
-      <c r="D48" t="s">
-        <v>147</v>
-      </c>
       <c r="E48" t="s">
+        <v>270</v>
+      </c>
+      <c r="F48" t="s">
         <v>271</v>
       </c>
-      <c r="F48" t="s">
-        <v>272</v>
-      </c>
       <c r="G48" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
@@ -2410,19 +2413,19 @@
         <v>4</v>
       </c>
       <c r="C49" t="s">
+        <v>147</v>
+      </c>
+      <c r="D49" t="s">
         <v>148</v>
       </c>
-      <c r="D49" t="s">
-        <v>149</v>
-      </c>
       <c r="E49" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F49" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G49" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
@@ -2433,19 +2436,19 @@
         <v>34</v>
       </c>
       <c r="C50" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D50" t="s">
+        <v>149</v>
+      </c>
+      <c r="E50" t="s">
+        <v>273</v>
+      </c>
+      <c r="F50" t="s">
+        <v>258</v>
+      </c>
+      <c r="G50" t="s">
         <v>150</v>
-      </c>
-      <c r="E50" t="s">
-        <v>274</v>
-      </c>
-      <c r="F50" t="s">
-        <v>259</v>
-      </c>
-      <c r="G50" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
@@ -2456,19 +2459,19 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
+        <v>151</v>
+      </c>
+      <c r="D51" t="s">
         <v>152</v>
       </c>
-      <c r="D51" t="s">
-        <v>153</v>
-      </c>
       <c r="E51" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F51" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G51" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
@@ -2479,19 +2482,19 @@
         <v>1</v>
       </c>
       <c r="C52" t="s">
+        <v>153</v>
+      </c>
+      <c r="D52" t="s">
         <v>154</v>
       </c>
-      <c r="D52" t="s">
-        <v>155</v>
-      </c>
       <c r="E52" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F52" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G52" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
@@ -2502,19 +2505,19 @@
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D53" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E53" t="s">
+        <v>276</v>
+      </c>
+      <c r="F53" t="s">
         <v>277</v>
       </c>
-      <c r="F53" t="s">
-        <v>278</v>
-      </c>
       <c r="G53" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
@@ -2525,19 +2528,19 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
+        <v>240</v>
+      </c>
+      <c r="D54" t="s">
+        <v>156</v>
+      </c>
+      <c r="E54" t="s">
+        <v>278</v>
+      </c>
+      <c r="F54" t="s">
+        <v>271</v>
+      </c>
+      <c r="G54" t="s">
         <v>241</v>
-      </c>
-      <c r="D54" t="s">
-        <v>157</v>
-      </c>
-      <c r="E54" t="s">
-        <v>279</v>
-      </c>
-      <c r="F54" t="s">
-        <v>272</v>
-      </c>
-      <c r="G54" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
@@ -2548,19 +2551,19 @@
         <v>9</v>
       </c>
       <c r="C55" t="s">
+        <v>235</v>
+      </c>
+      <c r="D55" t="s">
+        <v>157</v>
+      </c>
+      <c r="E55" t="s">
+        <v>279</v>
+      </c>
+      <c r="F55" t="s">
+        <v>258</v>
+      </c>
+      <c r="G55" t="s">
         <v>236</v>
-      </c>
-      <c r="D55" t="s">
-        <v>158</v>
-      </c>
-      <c r="E55" t="s">
-        <v>280</v>
-      </c>
-      <c r="F55" t="s">
-        <v>259</v>
-      </c>
-      <c r="G55" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
@@ -2571,19 +2574,19 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D56" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E56" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F56" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G56" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
@@ -2594,19 +2597,19 @@
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D57" t="s">
+        <v>243</v>
+      </c>
+      <c r="E57" t="s">
+        <v>281</v>
+      </c>
+      <c r="F57" t="s">
+        <v>271</v>
+      </c>
+      <c r="G57" t="s">
         <v>244</v>
-      </c>
-      <c r="E57" t="s">
-        <v>282</v>
-      </c>
-      <c r="F57" t="s">
-        <v>272</v>
-      </c>
-      <c r="G57" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
@@ -2617,19 +2620,19 @@
         <v>1</v>
       </c>
       <c r="C58" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D58" t="s">
+        <v>245</v>
+      </c>
+      <c r="E58" t="s">
+        <v>282</v>
+      </c>
+      <c r="F58" t="s">
+        <v>271</v>
+      </c>
+      <c r="G58" t="s">
         <v>246</v>
-      </c>
-      <c r="E58" t="s">
-        <v>283</v>
-      </c>
-      <c r="F58" t="s">
-        <v>272</v>
-      </c>
-      <c r="G58" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
@@ -2640,19 +2643,19 @@
         <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D59" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E59" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F59" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G59" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
@@ -2663,19 +2666,19 @@
         <v>3</v>
       </c>
       <c r="C60" t="s">
+        <v>237</v>
+      </c>
+      <c r="D60" t="s">
+        <v>162</v>
+      </c>
+      <c r="E60" t="s">
+        <v>285</v>
+      </c>
+      <c r="F60" t="s">
+        <v>271</v>
+      </c>
+      <c r="G60" t="s">
         <v>238</v>
-      </c>
-      <c r="D60" t="s">
-        <v>163</v>
-      </c>
-      <c r="E60" t="s">
-        <v>286</v>
-      </c>
-      <c r="F60" t="s">
-        <v>272</v>
-      </c>
-      <c r="G60" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
@@ -2686,19 +2689,19 @@
         <v>1</v>
       </c>
       <c r="C61" t="s">
+        <v>163</v>
+      </c>
+      <c r="D61" t="s">
         <v>164</v>
       </c>
-      <c r="D61" t="s">
-        <v>165</v>
-      </c>
       <c r="E61" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F61" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G61" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
@@ -2709,10 +2712,10 @@
         <v>9</v>
       </c>
       <c r="C62" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D62" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E62" t="s">
         <v>9</v>
@@ -2732,19 +2735,19 @@
         <v>1</v>
       </c>
       <c r="C63" t="s">
+        <v>166</v>
+      </c>
+      <c r="D63" t="s">
         <v>167</v>
       </c>
-      <c r="D63" t="s">
+      <c r="E63" t="s">
         <v>168</v>
       </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
         <v>169</v>
       </c>
-      <c r="F63" t="s">
+      <c r="G63" t="s">
         <v>170</v>
-      </c>
-      <c r="G63" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
@@ -2755,10 +2758,10 @@
         <v>1</v>
       </c>
       <c r="C64" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D64" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E64" t="s">
         <v>9</v>
@@ -2778,19 +2781,19 @@
         <v>1</v>
       </c>
       <c r="C65" t="s">
+        <v>172</v>
+      </c>
+      <c r="D65" t="s">
         <v>173</v>
       </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
+        <v>248</v>
+      </c>
+      <c r="F65" t="s">
+        <v>249</v>
+      </c>
+      <c r="G65" t="s">
         <v>174</v>
-      </c>
-      <c r="E65" t="s">
-        <v>249</v>
-      </c>
-      <c r="F65" t="s">
-        <v>250</v>
-      </c>
-      <c r="G65" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
@@ -2801,19 +2804,19 @@
         <v>4</v>
       </c>
       <c r="C66" t="s">
+        <v>175</v>
+      </c>
+      <c r="D66" t="s">
+        <v>173</v>
+      </c>
+      <c r="E66" t="s">
         <v>176</v>
       </c>
-      <c r="D66" t="s">
-        <v>174</v>
-      </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>177</v>
       </c>
-      <c r="F66" t="s">
+      <c r="G66" t="s">
         <v>178</v>
-      </c>
-      <c r="G66" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
@@ -2824,19 +2827,19 @@
         <v>1</v>
       </c>
       <c r="C67" t="s">
+        <v>179</v>
+      </c>
+      <c r="D67" t="s">
         <v>180</v>
       </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
+        <v>180</v>
+      </c>
+      <c r="F67" t="s">
+        <v>104</v>
+      </c>
+      <c r="G67" t="s">
         <v>181</v>
-      </c>
-      <c r="E67" t="s">
-        <v>181</v>
-      </c>
-      <c r="F67" t="s">
-        <v>105</v>
-      </c>
-      <c r="G67" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
@@ -2847,19 +2850,19 @@
         <v>2</v>
       </c>
       <c r="C68" t="s">
+        <v>182</v>
+      </c>
+      <c r="D68" t="s">
         <v>183</v>
       </c>
-      <c r="D68" t="s">
+      <c r="E68" t="s">
+        <v>183</v>
+      </c>
+      <c r="F68" t="s">
+        <v>104</v>
+      </c>
+      <c r="G68" t="s">
         <v>184</v>
-      </c>
-      <c r="E68" t="s">
-        <v>184</v>
-      </c>
-      <c r="F68" t="s">
-        <v>105</v>
-      </c>
-      <c r="G68" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
@@ -2870,19 +2873,19 @@
         <v>3</v>
       </c>
       <c r="C69" t="s">
+        <v>185</v>
+      </c>
+      <c r="D69" t="s">
         <v>186</v>
       </c>
-      <c r="D69" t="s">
+      <c r="E69" t="s">
+        <v>186</v>
+      </c>
+      <c r="F69" t="s">
         <v>187</v>
       </c>
-      <c r="E69" t="s">
-        <v>187</v>
-      </c>
-      <c r="F69" t="s">
+      <c r="G69" t="s">
         <v>188</v>
-      </c>
-      <c r="G69" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
@@ -2893,19 +2896,19 @@
         <v>1</v>
       </c>
       <c r="C70" t="s">
+        <v>189</v>
+      </c>
+      <c r="D70" t="s">
         <v>190</v>
       </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
         <v>191</v>
       </c>
-      <c r="E70" t="s">
+      <c r="F70" t="s">
+        <v>104</v>
+      </c>
+      <c r="G70" t="s">
         <v>192</v>
-      </c>
-      <c r="F70" t="s">
-        <v>105</v>
-      </c>
-      <c r="G70" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
@@ -2916,19 +2919,19 @@
         <v>1</v>
       </c>
       <c r="C71" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D71" t="s">
+        <v>193</v>
+      </c>
+      <c r="E71" t="s">
+        <v>193</v>
+      </c>
+      <c r="F71" t="s">
+        <v>104</v>
+      </c>
+      <c r="G71" t="s">
         <v>194</v>
-      </c>
-      <c r="E71" t="s">
-        <v>194</v>
-      </c>
-      <c r="F71" t="s">
-        <v>105</v>
-      </c>
-      <c r="G71" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
@@ -2939,10 +2942,10 @@
         <v>1</v>
       </c>
       <c r="C72" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D72" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E72" t="s">
         <v>9</v>
@@ -2962,19 +2965,19 @@
         <v>1</v>
       </c>
       <c r="C73" t="s">
+        <v>195</v>
+      </c>
+      <c r="D73" t="s">
         <v>196</v>
       </c>
-      <c r="D73" t="s">
+      <c r="E73" t="s">
+        <v>196</v>
+      </c>
+      <c r="F73" t="s">
+        <v>104</v>
+      </c>
+      <c r="G73" t="s">
         <v>197</v>
-      </c>
-      <c r="E73" t="s">
-        <v>197</v>
-      </c>
-      <c r="F73" t="s">
-        <v>105</v>
-      </c>
-      <c r="G73" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
@@ -2985,19 +2988,19 @@
         <v>1</v>
       </c>
       <c r="C74" t="s">
+        <v>198</v>
+      </c>
+      <c r="D74" t="s">
         <v>199</v>
       </c>
-      <c r="D74" t="s">
-        <v>200</v>
-      </c>
       <c r="E74" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F74" t="s">
         <v>17</v>
       </c>
       <c r="G74" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
@@ -3008,19 +3011,19 @@
         <v>1</v>
       </c>
       <c r="C75" t="s">
+        <v>201</v>
+      </c>
+      <c r="D75" t="s">
         <v>202</v>
       </c>
-      <c r="D75" t="s">
+      <c r="E75" t="s">
+        <v>202</v>
+      </c>
+      <c r="F75" t="s">
         <v>203</v>
       </c>
-      <c r="E75" t="s">
-        <v>203</v>
-      </c>
-      <c r="F75" t="s">
+      <c r="G75" t="s">
         <v>204</v>
-      </c>
-      <c r="G75" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
@@ -3031,19 +3034,19 @@
         <v>1</v>
       </c>
       <c r="C76" t="s">
+        <v>205</v>
+      </c>
+      <c r="D76" t="s">
         <v>206</v>
       </c>
-      <c r="D76" t="s">
+      <c r="E76" t="s">
+        <v>206</v>
+      </c>
+      <c r="F76" t="s">
+        <v>203</v>
+      </c>
+      <c r="G76" t="s">
         <v>207</v>
-      </c>
-      <c r="E76" t="s">
-        <v>207</v>
-      </c>
-      <c r="F76" t="s">
-        <v>204</v>
-      </c>
-      <c r="G76" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
@@ -3054,19 +3057,19 @@
         <v>1</v>
       </c>
       <c r="C77" t="s">
+        <v>208</v>
+      </c>
+      <c r="D77" t="s">
         <v>209</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
         <v>210</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
         <v>211</v>
       </c>
-      <c r="F77" t="s">
+      <c r="G77" t="s">
         <v>212</v>
-      </c>
-      <c r="G77" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
@@ -3077,19 +3080,19 @@
         <v>1</v>
       </c>
       <c r="C78" t="s">
+        <v>213</v>
+      </c>
+      <c r="D78" t="s">
         <v>214</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78" t="s">
         <v>215</v>
       </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
+        <v>211</v>
+      </c>
+      <c r="G78" t="s">
         <v>216</v>
-      </c>
-      <c r="F78" t="s">
-        <v>212</v>
-      </c>
-      <c r="G78" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
@@ -3100,7 +3103,7 @@
         <v>4</v>
       </c>
       <c r="C79" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D79" t="s">
         <v>19</v>
@@ -3112,7 +3115,7 @@
         <v>21</v>
       </c>
       <c r="G79" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>

--- a/TURFv6/revC/TURFv6_revC_BOM_041525.xlsx
+++ b/TURFv6/revC/TURFv6_revC_BOM_041525.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="V:\pueo-daq-design\TURFv6\revC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EECFFCB-E100-435C-AE6A-156FCECF6241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC5FD8E-8B9F-4092-BD39-6F825523019F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D3B74482-F8A5-4E82-A69B-8579953A21D8}"/>
   </bookViews>
@@ -266,15 +266,9 @@
     <t>DT1446</t>
   </si>
   <si>
-    <t>DT1446-04TS-7</t>
-  </si>
-  <si>
     <t>Diodes, Inc.</t>
   </si>
   <si>
-    <t>ESD Suppressor Diode Array Uni-Dir 5V Automotive 6-Pin TSOT-26 T/R</t>
-  </si>
-  <si>
     <t>J17</t>
   </si>
   <si>
@@ -921,6 +915,12 @@
   </si>
   <si>
     <t>MOSFET N-CH 60V 115MA SOT23-3</t>
+  </si>
+  <si>
+    <t>DT1446-04S-7</t>
+  </si>
+  <si>
+    <t>8.5V Clamp 4.7A (8/20µs) Ipp Tvs Diode Surface Mount SOT-363</t>
   </si>
 </sst>
 </file>
@@ -1404,7 +1404,7 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D5" t="s">
         <v>19</v>
@@ -1413,10 +1413,10 @@
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1502,7 +1502,7 @@
         <v>33</v>
       </c>
       <c r="E9" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F9" t="s">
         <v>17</v>
@@ -1631,19 +1631,19 @@
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D15" t="s">
         <v>49</v>
       </c>
       <c r="E15" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F15" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G15" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -1654,16 +1654,16 @@
         <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D16" t="s">
         <v>49</v>
       </c>
       <c r="E16" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G16" t="s">
         <v>50</v>
@@ -1677,19 +1677,19 @@
         <v>3</v>
       </c>
       <c r="C17" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D17" t="s">
         <v>52</v>
       </c>
       <c r="E17" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F17" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G17" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -1706,13 +1706,13 @@
         <v>54</v>
       </c>
       <c r="E18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F18" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G18" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -1723,16 +1723,16 @@
         <v>6</v>
       </c>
       <c r="C19" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D19" t="s">
         <v>55</v>
       </c>
       <c r="E19" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F19" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G19" t="s">
         <v>56</v>
@@ -1746,19 +1746,19 @@
         <v>2</v>
       </c>
       <c r="C20" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D20" t="s">
         <v>57</v>
       </c>
       <c r="E20" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F20" t="s">
         <v>51</v>
       </c>
       <c r="G20" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -1769,19 +1769,19 @@
         <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D21" t="s">
         <v>58</v>
       </c>
       <c r="E21" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F21" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G21" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -1798,13 +1798,13 @@
         <v>60</v>
       </c>
       <c r="E22" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F22" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G22" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -1913,13 +1913,13 @@
         <v>75</v>
       </c>
       <c r="E27" t="s">
+        <v>293</v>
+      </c>
+      <c r="F27" t="s">
         <v>76</v>
       </c>
-      <c r="F27" t="s">
-        <v>77</v>
-      </c>
       <c r="G27" t="s">
-        <v>78</v>
+        <v>294</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -1930,19 +1930,19 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
+        <v>77</v>
+      </c>
+      <c r="D28" t="s">
+        <v>78</v>
+      </c>
+      <c r="E28" t="s">
+        <v>78</v>
+      </c>
+      <c r="F28" t="s">
         <v>79</v>
       </c>
-      <c r="D28" t="s">
+      <c r="G28" t="s">
         <v>80</v>
-      </c>
-      <c r="E28" t="s">
-        <v>80</v>
-      </c>
-      <c r="F28" t="s">
-        <v>81</v>
-      </c>
-      <c r="G28" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -1953,19 +1953,19 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D29" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E29" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F29" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G29" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -1976,19 +1976,19 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
+        <v>83</v>
+      </c>
+      <c r="D30" t="s">
+        <v>84</v>
+      </c>
+      <c r="E30" t="s">
         <v>85</v>
       </c>
-      <c r="D30" t="s">
+      <c r="F30" t="s">
         <v>86</v>
       </c>
-      <c r="E30" t="s">
+      <c r="G30" t="s">
         <v>87</v>
-      </c>
-      <c r="F30" t="s">
-        <v>88</v>
-      </c>
-      <c r="G30" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -1999,10 +1999,10 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D31" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E31" t="s">
         <v>9</v>
@@ -2022,10 +2022,10 @@
         <v>2</v>
       </c>
       <c r="C32" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D32" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
@@ -2045,19 +2045,19 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
+        <v>92</v>
+      </c>
+      <c r="D33" t="s">
+        <v>93</v>
+      </c>
+      <c r="E33" t="s">
         <v>94</v>
       </c>
-      <c r="D33" t="s">
+      <c r="F33" t="s">
         <v>95</v>
       </c>
-      <c r="E33" t="s">
+      <c r="G33" t="s">
         <v>96</v>
-      </c>
-      <c r="F33" t="s">
-        <v>97</v>
-      </c>
-      <c r="G33" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -2068,19 +2068,19 @@
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D34" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E34" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F34" t="s">
         <v>41</v>
       </c>
       <c r="G34" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -2091,19 +2091,19 @@
         <v>1</v>
       </c>
       <c r="C35" t="s">
+        <v>100</v>
+      </c>
+      <c r="D35" t="s">
+        <v>101</v>
+      </c>
+      <c r="E35" t="s">
+        <v>289</v>
+      </c>
+      <c r="F35" t="s">
         <v>102</v>
       </c>
-      <c r="D35" t="s">
+      <c r="G35" t="s">
         <v>103</v>
-      </c>
-      <c r="E35" t="s">
-        <v>291</v>
-      </c>
-      <c r="F35" t="s">
-        <v>104</v>
-      </c>
-      <c r="G35" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -2114,19 +2114,19 @@
         <v>1</v>
       </c>
       <c r="C36" t="s">
+        <v>104</v>
+      </c>
+      <c r="D36" t="s">
+        <v>105</v>
+      </c>
+      <c r="E36" t="s">
         <v>106</v>
-      </c>
-      <c r="D36" t="s">
-        <v>107</v>
-      </c>
-      <c r="E36" t="s">
-        <v>108</v>
       </c>
       <c r="F36" t="s">
         <v>17</v>
       </c>
       <c r="G36" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -2137,19 +2137,19 @@
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D37" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E37" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F37" t="s">
         <v>17</v>
       </c>
       <c r="G37" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -2160,10 +2160,10 @@
         <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D38" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E38" t="s">
         <v>9</v>
@@ -2183,10 +2183,10 @@
         <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D39" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E39" t="s">
         <v>9</v>
@@ -2206,19 +2206,19 @@
         <v>1</v>
       </c>
       <c r="C40" t="s">
+        <v>115</v>
+      </c>
+      <c r="D40" t="s">
+        <v>116</v>
+      </c>
+      <c r="E40" t="s">
+        <v>116</v>
+      </c>
+      <c r="F40" t="s">
         <v>117</v>
       </c>
-      <c r="D40" t="s">
+      <c r="G40" t="s">
         <v>118</v>
-      </c>
-      <c r="E40" t="s">
-        <v>118</v>
-      </c>
-      <c r="F40" t="s">
-        <v>119</v>
-      </c>
-      <c r="G40" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
@@ -2229,10 +2229,10 @@
         <v>28</v>
       </c>
       <c r="C41" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D41" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E41" t="s">
         <v>9</v>
@@ -2252,19 +2252,19 @@
         <v>1</v>
       </c>
       <c r="C42" t="s">
+        <v>121</v>
+      </c>
+      <c r="D42" t="s">
+        <v>122</v>
+      </c>
+      <c r="E42" t="s">
+        <v>122</v>
+      </c>
+      <c r="F42" t="s">
         <v>123</v>
       </c>
-      <c r="D42" t="s">
+      <c r="G42" t="s">
         <v>124</v>
-      </c>
-      <c r="E42" t="s">
-        <v>124</v>
-      </c>
-      <c r="F42" t="s">
-        <v>125</v>
-      </c>
-      <c r="G42" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -2275,19 +2275,19 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
+        <v>125</v>
+      </c>
+      <c r="D43" t="s">
+        <v>126</v>
+      </c>
+      <c r="E43" t="s">
         <v>127</v>
-      </c>
-      <c r="D43" t="s">
-        <v>128</v>
-      </c>
-      <c r="E43" t="s">
-        <v>129</v>
       </c>
       <c r="F43" t="s">
         <v>51</v>
       </c>
       <c r="G43" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -2298,19 +2298,19 @@
         <v>1</v>
       </c>
       <c r="C44" t="s">
+        <v>129</v>
+      </c>
+      <c r="D44" t="s">
+        <v>130</v>
+      </c>
+      <c r="E44" t="s">
         <v>131</v>
       </c>
-      <c r="D44" t="s">
+      <c r="F44" t="s">
         <v>132</v>
       </c>
-      <c r="E44" t="s">
+      <c r="G44" t="s">
         <v>133</v>
-      </c>
-      <c r="F44" t="s">
-        <v>134</v>
-      </c>
-      <c r="G44" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -2321,19 +2321,19 @@
         <v>1</v>
       </c>
       <c r="C45" t="s">
+        <v>134</v>
+      </c>
+      <c r="D45" t="s">
+        <v>135</v>
+      </c>
+      <c r="E45" t="s">
         <v>136</v>
       </c>
-      <c r="D45" t="s">
+      <c r="F45" t="s">
+        <v>132</v>
+      </c>
+      <c r="G45" t="s">
         <v>137</v>
-      </c>
-      <c r="E45" t="s">
-        <v>138</v>
-      </c>
-      <c r="F45" t="s">
-        <v>134</v>
-      </c>
-      <c r="G45" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -2344,19 +2344,19 @@
         <v>2</v>
       </c>
       <c r="C46" t="s">
+        <v>138</v>
+      </c>
+      <c r="D46" t="s">
+        <v>139</v>
+      </c>
+      <c r="E46" t="s">
+        <v>288</v>
+      </c>
+      <c r="F46" t="s">
+        <v>79</v>
+      </c>
+      <c r="G46" t="s">
         <v>140</v>
-      </c>
-      <c r="D46" t="s">
-        <v>141</v>
-      </c>
-      <c r="E46" t="s">
-        <v>290</v>
-      </c>
-      <c r="F46" t="s">
-        <v>81</v>
-      </c>
-      <c r="G46" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -2367,19 +2367,19 @@
         <v>5</v>
       </c>
       <c r="C47" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D47" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E47" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F47" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G47" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
@@ -2390,19 +2390,19 @@
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D48" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E48" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F48" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G48" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
@@ -2413,19 +2413,19 @@
         <v>4</v>
       </c>
       <c r="C49" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D49" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E49" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F49" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G49" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
@@ -2436,19 +2436,19 @@
         <v>34</v>
       </c>
       <c r="C50" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D50" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E50" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F50" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G50" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
@@ -2459,19 +2459,19 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D51" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E51" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F51" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G51" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
@@ -2482,19 +2482,19 @@
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D52" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E52" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F52" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G52" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
@@ -2505,19 +2505,19 @@
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D53" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E53" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F53" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G53" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
@@ -2528,19 +2528,19 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D54" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E54" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F54" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G54" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
@@ -2551,19 +2551,19 @@
         <v>9</v>
       </c>
       <c r="C55" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D55" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E55" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F55" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G55" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
@@ -2574,19 +2574,19 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D56" t="s">
+        <v>248</v>
+      </c>
+      <c r="E56" t="s">
+        <v>278</v>
+      </c>
+      <c r="F56" t="s">
+        <v>269</v>
+      </c>
+      <c r="G56" t="s">
         <v>250</v>
-      </c>
-      <c r="E56" t="s">
-        <v>280</v>
-      </c>
-      <c r="F56" t="s">
-        <v>271</v>
-      </c>
-      <c r="G56" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
@@ -2597,19 +2597,19 @@
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D57" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E57" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F57" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G57" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
@@ -2620,19 +2620,19 @@
         <v>1</v>
       </c>
       <c r="C58" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D58" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E58" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F58" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G58" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
@@ -2643,19 +2643,19 @@
         <v>1</v>
       </c>
       <c r="C59" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D59" t="s">
+        <v>249</v>
+      </c>
+      <c r="E59" t="s">
+        <v>282</v>
+      </c>
+      <c r="F59" t="s">
+        <v>269</v>
+      </c>
+      <c r="G59" t="s">
         <v>251</v>
-      </c>
-      <c r="E59" t="s">
-        <v>284</v>
-      </c>
-      <c r="F59" t="s">
-        <v>271</v>
-      </c>
-      <c r="G59" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
@@ -2666,19 +2666,19 @@
         <v>3</v>
       </c>
       <c r="C60" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D60" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E60" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F60" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G60" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
@@ -2689,19 +2689,19 @@
         <v>1</v>
       </c>
       <c r="C61" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D61" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E61" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F61" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G61" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
@@ -2712,10 +2712,10 @@
         <v>9</v>
       </c>
       <c r="C62" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D62" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E62" t="s">
         <v>9</v>
@@ -2735,19 +2735,19 @@
         <v>1</v>
       </c>
       <c r="C63" t="s">
+        <v>164</v>
+      </c>
+      <c r="D63" t="s">
+        <v>165</v>
+      </c>
+      <c r="E63" t="s">
         <v>166</v>
       </c>
-      <c r="D63" t="s">
+      <c r="F63" t="s">
         <v>167</v>
       </c>
-      <c r="E63" t="s">
+      <c r="G63" t="s">
         <v>168</v>
-      </c>
-      <c r="F63" t="s">
-        <v>169</v>
-      </c>
-      <c r="G63" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
@@ -2758,10 +2758,10 @@
         <v>1</v>
       </c>
       <c r="C64" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D64" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E64" t="s">
         <v>9</v>
@@ -2781,19 +2781,19 @@
         <v>1</v>
       </c>
       <c r="C65" t="s">
+        <v>170</v>
+      </c>
+      <c r="D65" t="s">
+        <v>171</v>
+      </c>
+      <c r="E65" t="s">
+        <v>246</v>
+      </c>
+      <c r="F65" t="s">
+        <v>247</v>
+      </c>
+      <c r="G65" t="s">
         <v>172</v>
-      </c>
-      <c r="D65" t="s">
-        <v>173</v>
-      </c>
-      <c r="E65" t="s">
-        <v>248</v>
-      </c>
-      <c r="F65" t="s">
-        <v>249</v>
-      </c>
-      <c r="G65" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
@@ -2804,19 +2804,19 @@
         <v>4</v>
       </c>
       <c r="C66" t="s">
+        <v>173</v>
+      </c>
+      <c r="D66" t="s">
+        <v>171</v>
+      </c>
+      <c r="E66" t="s">
+        <v>174</v>
+      </c>
+      <c r="F66" t="s">
         <v>175</v>
       </c>
-      <c r="D66" t="s">
-        <v>173</v>
-      </c>
-      <c r="E66" t="s">
+      <c r="G66" t="s">
         <v>176</v>
-      </c>
-      <c r="F66" t="s">
-        <v>177</v>
-      </c>
-      <c r="G66" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
@@ -2827,19 +2827,19 @@
         <v>1</v>
       </c>
       <c r="C67" t="s">
+        <v>177</v>
+      </c>
+      <c r="D67" t="s">
+        <v>178</v>
+      </c>
+      <c r="E67" t="s">
+        <v>178</v>
+      </c>
+      <c r="F67" t="s">
+        <v>102</v>
+      </c>
+      <c r="G67" t="s">
         <v>179</v>
-      </c>
-      <c r="D67" t="s">
-        <v>180</v>
-      </c>
-      <c r="E67" t="s">
-        <v>180</v>
-      </c>
-      <c r="F67" t="s">
-        <v>104</v>
-      </c>
-      <c r="G67" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
@@ -2850,19 +2850,19 @@
         <v>2</v>
       </c>
       <c r="C68" t="s">
+        <v>180</v>
+      </c>
+      <c r="D68" t="s">
+        <v>181</v>
+      </c>
+      <c r="E68" t="s">
+        <v>181</v>
+      </c>
+      <c r="F68" t="s">
+        <v>102</v>
+      </c>
+      <c r="G68" t="s">
         <v>182</v>
-      </c>
-      <c r="D68" t="s">
-        <v>183</v>
-      </c>
-      <c r="E68" t="s">
-        <v>183</v>
-      </c>
-      <c r="F68" t="s">
-        <v>104</v>
-      </c>
-      <c r="G68" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
@@ -2873,19 +2873,19 @@
         <v>3</v>
       </c>
       <c r="C69" t="s">
+        <v>183</v>
+      </c>
+      <c r="D69" t="s">
+        <v>184</v>
+      </c>
+      <c r="E69" t="s">
+        <v>184</v>
+      </c>
+      <c r="F69" t="s">
         <v>185</v>
       </c>
-      <c r="D69" t="s">
+      <c r="G69" t="s">
         <v>186</v>
-      </c>
-      <c r="E69" t="s">
-        <v>186</v>
-      </c>
-      <c r="F69" t="s">
-        <v>187</v>
-      </c>
-      <c r="G69" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
@@ -2896,19 +2896,19 @@
         <v>1</v>
       </c>
       <c r="C70" t="s">
+        <v>187</v>
+      </c>
+      <c r="D70" t="s">
+        <v>188</v>
+      </c>
+      <c r="E70" t="s">
         <v>189</v>
       </c>
-      <c r="D70" t="s">
+      <c r="F70" t="s">
+        <v>102</v>
+      </c>
+      <c r="G70" t="s">
         <v>190</v>
-      </c>
-      <c r="E70" t="s">
-        <v>191</v>
-      </c>
-      <c r="F70" t="s">
-        <v>104</v>
-      </c>
-      <c r="G70" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
@@ -2919,19 +2919,19 @@
         <v>1</v>
       </c>
       <c r="C71" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D71" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E71" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F71" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G71" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
@@ -2942,10 +2942,10 @@
         <v>1</v>
       </c>
       <c r="C72" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D72" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E72" t="s">
         <v>9</v>
@@ -2965,19 +2965,19 @@
         <v>1</v>
       </c>
       <c r="C73" t="s">
+        <v>193</v>
+      </c>
+      <c r="D73" t="s">
+        <v>194</v>
+      </c>
+      <c r="E73" t="s">
+        <v>194</v>
+      </c>
+      <c r="F73" t="s">
+        <v>102</v>
+      </c>
+      <c r="G73" t="s">
         <v>195</v>
-      </c>
-      <c r="D73" t="s">
-        <v>196</v>
-      </c>
-      <c r="E73" t="s">
-        <v>196</v>
-      </c>
-      <c r="F73" t="s">
-        <v>104</v>
-      </c>
-      <c r="G73" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
@@ -2988,19 +2988,19 @@
         <v>1</v>
       </c>
       <c r="C74" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D74" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E74" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F74" t="s">
         <v>17</v>
       </c>
       <c r="G74" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
@@ -3011,19 +3011,19 @@
         <v>1</v>
       </c>
       <c r="C75" t="s">
+        <v>199</v>
+      </c>
+      <c r="D75" t="s">
+        <v>200</v>
+      </c>
+      <c r="E75" t="s">
+        <v>200</v>
+      </c>
+      <c r="F75" t="s">
         <v>201</v>
       </c>
-      <c r="D75" t="s">
+      <c r="G75" t="s">
         <v>202</v>
-      </c>
-      <c r="E75" t="s">
-        <v>202</v>
-      </c>
-      <c r="F75" t="s">
-        <v>203</v>
-      </c>
-      <c r="G75" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
@@ -3034,19 +3034,19 @@
         <v>1</v>
       </c>
       <c r="C76" t="s">
+        <v>203</v>
+      </c>
+      <c r="D76" t="s">
+        <v>204</v>
+      </c>
+      <c r="E76" t="s">
+        <v>204</v>
+      </c>
+      <c r="F76" t="s">
+        <v>201</v>
+      </c>
+      <c r="G76" t="s">
         <v>205</v>
-      </c>
-      <c r="D76" t="s">
-        <v>206</v>
-      </c>
-      <c r="E76" t="s">
-        <v>206</v>
-      </c>
-      <c r="F76" t="s">
-        <v>203</v>
-      </c>
-      <c r="G76" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
@@ -3057,19 +3057,19 @@
         <v>1</v>
       </c>
       <c r="C77" t="s">
+        <v>206</v>
+      </c>
+      <c r="D77" t="s">
+        <v>207</v>
+      </c>
+      <c r="E77" t="s">
         <v>208</v>
       </c>
-      <c r="D77" t="s">
+      <c r="F77" t="s">
         <v>209</v>
       </c>
-      <c r="E77" t="s">
+      <c r="G77" t="s">
         <v>210</v>
-      </c>
-      <c r="F77" t="s">
-        <v>211</v>
-      </c>
-      <c r="G77" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
@@ -3080,19 +3080,19 @@
         <v>1</v>
       </c>
       <c r="C78" t="s">
+        <v>211</v>
+      </c>
+      <c r="D78" t="s">
+        <v>212</v>
+      </c>
+      <c r="E78" t="s">
         <v>213</v>
       </c>
-      <c r="D78" t="s">
+      <c r="F78" t="s">
+        <v>209</v>
+      </c>
+      <c r="G78" t="s">
         <v>214</v>
-      </c>
-      <c r="E78" t="s">
-        <v>215</v>
-      </c>
-      <c r="F78" t="s">
-        <v>211</v>
-      </c>
-      <c r="G78" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
@@ -3103,7 +3103,7 @@
         <v>4</v>
       </c>
       <c r="C79" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D79" t="s">
         <v>19</v>
@@ -3115,7 +3115,7 @@
         <v>21</v>
       </c>
       <c r="G79" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
